--- a/Excel/整理.xlsx
+++ b/Excel/整理.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R49"/>
+  <dimension ref="A1:U59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,6 +505,21 @@
       <c r="R1" t="inlineStr">
         <is>
           <t>2026/10/19</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>2026/10/22</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>2026/10/27</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>2026/10/29</t>
         </is>
       </c>
     </row>
@@ -537,6 +552,9 @@
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -567,6 +585,9 @@
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -595,6 +616,9 @@
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -643,6 +667,9 @@
         <v>22.97979797979798</v>
       </c>
       <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -691,6 +718,9 @@
         <v>21.81265147842947</v>
       </c>
       <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -739,6 +769,9 @@
         <v>21.77165354330709</v>
       </c>
       <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -787,6 +820,9 @@
         <v>25.39534883720931</v>
       </c>
       <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -835,6 +871,9 @@
         <v>26.66795171585667</v>
       </c>
       <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -883,6 +922,9 @@
         <v>25.89226519337017</v>
       </c>
       <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -915,6 +957,9 @@
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -947,6 +992,9 @@
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -979,6 +1027,9 @@
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1011,6 +1062,9 @@
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1043,6 +1097,9 @@
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1075,6 +1132,9 @@
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1107,6 +1167,11 @@
       <c r="R17" t="n">
         <v>62.2899720072452</v>
       </c>
+      <c r="S17" t="n">
+        <v>59.64811068856702</v>
+      </c>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1139,6 +1204,11 @@
       <c r="R18" t="n">
         <v>57.85353373840742</v>
       </c>
+      <c r="S18" t="n">
+        <v>90.45015105740183</v>
+      </c>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1171,6 +1241,11 @@
       <c r="R19" t="n">
         <v>46.98710442451642</v>
       </c>
+      <c r="S19" t="n">
+        <v>80.28426862925483</v>
+      </c>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1203,6 +1278,11 @@
       <c r="R20" t="n">
         <v>101.6992341130201</v>
       </c>
+      <c r="S20" t="n">
+        <v>109.8912386706949</v>
+      </c>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1235,6 +1315,11 @@
       <c r="R21" t="n">
         <v>121.2745411013567</v>
       </c>
+      <c r="S21" t="n">
+        <v>111.0028208744711</v>
+      </c>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1267,6 +1352,11 @@
       <c r="R22" t="n">
         <v>130.3864447086801</v>
       </c>
+      <c r="S22" t="n">
+        <v>106.6287018363231</v>
+      </c>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1297,6 +1387,9 @@
       <c r="R23" t="n">
         <v>61.28692949451989</v>
       </c>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1321,6 +1414,9 @@
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1345,6 +1441,9 @@
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1369,6 +1468,9 @@
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1393,6 +1495,9 @@
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1417,6 +1522,9 @@
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1441,6 +1549,9 @@
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1471,6 +1582,9 @@
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1497,32 +1611,25 @@
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>紙杯40度</t>
+          <t>空白升溫30</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="n">
-        <v>30.58688695879319</v>
-      </c>
-      <c r="G32" t="n">
-        <v>34.4622641509434</v>
-      </c>
-      <c r="H32" t="n">
-        <v>29.57897804546338</v>
-      </c>
-      <c r="I32" t="n">
-        <v>29.57897804546338</v>
-      </c>
-      <c r="J32" t="n">
-        <v>27.29595272889001</v>
-      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
@@ -1531,32 +1638,27 @@
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="n">
+        <v>21.84</v>
+      </c>
+      <c r="U32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>紙杯60度</t>
+          <t>空白升溫40</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="n">
-        <v>28.81852114035652</v>
-      </c>
-      <c r="G33" t="n">
-        <v>30.20695267235207</v>
-      </c>
-      <c r="H33" t="n">
-        <v>30.52339925592325</v>
-      </c>
-      <c r="I33" t="n">
-        <v>30.52339925592325</v>
-      </c>
-      <c r="J33" t="n">
-        <v>29.34516191584255</v>
-      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
@@ -1565,20 +1667,23 @@
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="n">
+        <v>28.69527483124397</v>
+      </c>
+      <c r="U33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>紙杯 80度</t>
+          <t>空白升溫50</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
-      <c r="F34" t="n">
-        <v>27.88512866355917</v>
-      </c>
+      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
@@ -1591,11 +1696,16 @@
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="n">
+        <v>31.45050970075633</v>
+      </c>
+      <c r="U34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>降溫30</t>
+          <t>空白升溫60</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1611,23 +1721,20 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
-      <c r="O35" t="n">
-        <v>53.52068617558022</v>
-      </c>
-      <c r="P35" t="n">
-        <v>61.12517362529617</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>66.17204119534021</v>
-      </c>
-      <c r="R35" t="n">
-        <v>55.40717150271291</v>
-      </c>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="n">
+        <v>28.72606263262814</v>
+      </c>
+      <c r="U35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>降溫40</t>
+          <t>空白升溫70</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1643,23 +1750,20 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
-      <c r="O36" t="n">
-        <v>60.82744842208269</v>
-      </c>
-      <c r="P36" t="n">
-        <v>52.76187167014131</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>60.49389747762408</v>
-      </c>
-      <c r="R36" t="n">
-        <v>48.69537815126051</v>
-      </c>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="n">
+        <v>31.54722569604423</v>
+      </c>
+      <c r="U36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>降溫50</t>
+          <t>空白升溫80</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -1675,23 +1779,20 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
-      <c r="O37" t="n">
-        <v>58.49895615866387</v>
-      </c>
-      <c r="P37" t="n">
-        <v>57.45000797321001</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>64.56985294117646</v>
-      </c>
-      <c r="R37" t="n">
-        <v>57.81784030053554</v>
-      </c>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="n">
+        <v>34.53839929876611</v>
+      </c>
+      <c r="U37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>降溫60</t>
+          <t>紙杯 40</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1702,28 +1803,25 @@
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+      <c r="J38" t="n">
+        <v>27.29595272889001</v>
+      </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
-      <c r="O38" t="n">
-        <v>58.22337100264487</v>
-      </c>
-      <c r="P38" t="n">
-        <v>47.14067369045853</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>51.36580516898609</v>
-      </c>
-      <c r="R38" t="n">
-        <v>43.42061944985922</v>
-      </c>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>降溫70</t>
+          <t>紙杯 60</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1734,35 +1832,34 @@
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+      <c r="J39" t="n">
+        <v>29.34516191584255</v>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
-      <c r="O39" t="n">
-        <v>65.78821052631579</v>
-      </c>
-      <c r="P39" t="n">
-        <v>60.58023284213954</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>66.49111825410252</v>
-      </c>
-      <c r="R39" t="n">
-        <v>74.71962616822429</v>
-      </c>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>降溫80</t>
+          <t>紙杯 80度</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+      <c r="F40" t="n">
+        <v>27.88512866355917</v>
+      </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
@@ -1771,81 +1868,88 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
-      <c r="O40" t="n">
-        <v>64.24555990994747</v>
-      </c>
-      <c r="P40" t="n">
-        <v>58.46295255679538</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>64.47891440501044</v>
-      </c>
-      <c r="R40" t="n">
-        <v>60.44460712542703</v>
-      </c>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>養樂多 磨過</t>
+          <t>紙杯40度</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
+      <c r="F41" t="n">
+        <v>30.58688695879319</v>
+      </c>
+      <c r="G41" t="n">
+        <v>34.4622641509434</v>
+      </c>
+      <c r="H41" t="n">
+        <v>29.57897804546338</v>
+      </c>
+      <c r="I41" t="n">
+        <v>29.57897804546338</v>
+      </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="n">
-        <v>17.09684161634927</v>
-      </c>
+      <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>養樂多30</t>
+          <t>紙杯60度</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
+      <c r="F42" t="n">
+        <v>28.81852114035652</v>
+      </c>
+      <c r="G42" t="n">
+        <v>30.20695267235207</v>
+      </c>
+      <c r="H42" t="n">
+        <v>30.52339925592325</v>
+      </c>
+      <c r="I42" t="n">
+        <v>30.52339925592325</v>
+      </c>
       <c r="J42" t="inlineStr"/>
-      <c r="K42" t="n">
-        <v>21.40972354623451</v>
-      </c>
-      <c r="L42" t="n">
-        <v>18.06566692050847</v>
-      </c>
-      <c r="M42" t="n">
-        <v>16.4728700069268</v>
-      </c>
-      <c r="N42" t="n">
-        <v>22.88219462964095</v>
-      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>養樂多40</t>
+          <t>降溫30</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -1857,27 +1961,32 @@
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="n">
-        <v>25.98774740810556</v>
-      </c>
-      <c r="L43" t="n">
-        <v>18.88962993566665</v>
-      </c>
-      <c r="M43" t="n">
-        <v>21.87420430433465</v>
-      </c>
-      <c r="N43" t="n">
-        <v>25.01096641535297</v>
-      </c>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="n">
+        <v>53.52068617558022</v>
+      </c>
+      <c r="P43" t="n">
+        <v>61.12517362529617</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>66.17204119534021</v>
+      </c>
+      <c r="R43" t="n">
+        <v>55.40717150271291</v>
+      </c>
+      <c r="S43" t="n">
+        <v>60.37073170731707</v>
+      </c>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>養樂多50</t>
+          <t>降溫40</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -1889,27 +1998,32 @@
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="n">
-        <v>27.74107142857143</v>
-      </c>
-      <c r="L44" t="n">
-        <v>27.74107142857143</v>
-      </c>
-      <c r="M44" t="n">
-        <v>25.05435392382971</v>
-      </c>
-      <c r="N44" t="n">
-        <v>28.12854309296819</v>
-      </c>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="n">
+        <v>60.82744842208269</v>
+      </c>
+      <c r="P44" t="n">
+        <v>52.76187167014131</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>60.49389747762408</v>
+      </c>
+      <c r="R44" t="n">
+        <v>48.69537815126051</v>
+      </c>
+      <c r="S44" t="n">
+        <v>54.95954844778929</v>
+      </c>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>養樂多60</t>
+          <t>降溫50</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -1921,27 +2035,32 @@
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
-      <c r="K45" t="n">
-        <v>26.69026548672566</v>
-      </c>
-      <c r="L45" t="n">
-        <v>26.69026548672566</v>
-      </c>
-      <c r="M45" t="n">
-        <v>24.51433180295322</v>
-      </c>
-      <c r="N45" t="n">
-        <v>28.81081081081081</v>
-      </c>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="n">
+        <v>58.49895615866387</v>
+      </c>
+      <c r="P45" t="n">
+        <v>57.45000797321001</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>64.56985294117646</v>
+      </c>
+      <c r="R45" t="n">
+        <v>57.81784030053554</v>
+      </c>
+      <c r="S45" t="n">
+        <v>59.58718861209963</v>
+      </c>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>養樂多70</t>
+          <t>降溫60</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -1953,27 +2072,32 @@
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
-      <c r="K46" t="n">
-        <v>28.37295633775726</v>
-      </c>
-      <c r="L46" t="n">
-        <v>28.37295633775726</v>
-      </c>
-      <c r="M46" t="n">
-        <v>23.49145246587135</v>
-      </c>
-      <c r="N46" t="n">
-        <v>28.0295358649789</v>
-      </c>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="n">
+        <v>58.22337100264487</v>
+      </c>
+      <c r="P46" t="n">
+        <v>47.14067369045853</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>51.36580516898609</v>
+      </c>
+      <c r="R46" t="n">
+        <v>43.42061944985922</v>
+      </c>
+      <c r="S46" t="n">
+        <v>54.03856041131105</v>
+      </c>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>養樂多80</t>
+          <t>降溫70</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -1985,27 +2109,32 @@
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
-      <c r="K47" t="n">
-        <v>26.46009715475365</v>
-      </c>
-      <c r="L47" t="n">
-        <v>26.46009715475365</v>
-      </c>
-      <c r="M47" t="n">
-        <v>23.64655172413793</v>
-      </c>
-      <c r="N47" t="n">
-        <v>28.89567905209607</v>
-      </c>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="n">
+        <v>65.78821052631579</v>
+      </c>
+      <c r="P47" t="n">
+        <v>60.58023284213954</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>66.49111825410252</v>
+      </c>
+      <c r="R47" t="n">
+        <v>74.71962616822429</v>
+      </c>
+      <c r="S47" t="n">
+        <v>58.94443102198598</v>
+      </c>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>養樂多空白</t>
+          <t>降溫80</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2019,21 +2148,30 @@
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="n">
-        <v>22.05240148157143</v>
-      </c>
-      <c r="N48" t="n">
-        <v>22.63891601562499</v>
-      </c>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="n">
+        <v>64.24555990994747</v>
+      </c>
+      <c r="P48" t="n">
+        <v>58.46295255679538</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>64.47891440501044</v>
+      </c>
+      <c r="R48" t="n">
+        <v>60.44460712542703</v>
+      </c>
+      <c r="S48" t="n">
+        <v>62.4921681780709</v>
+      </c>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>養樂多空白值</t>
+          <t>養樂多 磨過</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2045,11 +2183,9 @@
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
-      <c r="K49" t="n">
-        <v>27.51432208784214</v>
-      </c>
+      <c r="K49" t="inlineStr"/>
       <c r="L49" t="n">
-        <v>21.73751135331517</v>
+        <v>17.09684161634927</v>
       </c>
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
@@ -2057,6 +2193,335 @@
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>養樂多30</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="n">
+        <v>21.40972354623451</v>
+      </c>
+      <c r="L50" t="n">
+        <v>18.06566692050847</v>
+      </c>
+      <c r="M50" t="n">
+        <v>16.4728700069268</v>
+      </c>
+      <c r="N50" t="n">
+        <v>22.88219462964095</v>
+      </c>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>養樂多40</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="n">
+        <v>25.98774740810556</v>
+      </c>
+      <c r="L51" t="n">
+        <v>18.88962993566665</v>
+      </c>
+      <c r="M51" t="n">
+        <v>21.87420430433465</v>
+      </c>
+      <c r="N51" t="n">
+        <v>25.01096641535297</v>
+      </c>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>養樂多50</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="n">
+        <v>27.74107142857143</v>
+      </c>
+      <c r="L52" t="n">
+        <v>27.74107142857143</v>
+      </c>
+      <c r="M52" t="n">
+        <v>25.05435392382971</v>
+      </c>
+      <c r="N52" t="n">
+        <v>28.12854309296819</v>
+      </c>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>養樂多60</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="n">
+        <v>26.69026548672566</v>
+      </c>
+      <c r="L53" t="n">
+        <v>26.69026548672566</v>
+      </c>
+      <c r="M53" t="n">
+        <v>24.51433180295322</v>
+      </c>
+      <c r="N53" t="n">
+        <v>28.81081081081081</v>
+      </c>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>養樂多70</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="n">
+        <v>28.37295633775726</v>
+      </c>
+      <c r="L54" t="n">
+        <v>28.37295633775726</v>
+      </c>
+      <c r="M54" t="n">
+        <v>23.49145246587135</v>
+      </c>
+      <c r="N54" t="n">
+        <v>28.0295358649789</v>
+      </c>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>養樂多80</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="n">
+        <v>26.46009715475365</v>
+      </c>
+      <c r="L55" t="n">
+        <v>26.46009715475365</v>
+      </c>
+      <c r="M55" t="n">
+        <v>23.64655172413793</v>
+      </c>
+      <c r="N55" t="n">
+        <v>28.89567905209607</v>
+      </c>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>養樂多空白</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="n">
+        <v>22.05240148157143</v>
+      </c>
+      <c r="N56" t="n">
+        <v>22.63891601562499</v>
+      </c>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>養樂多空白值</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="n">
+        <v>27.51432208784214</v>
+      </c>
+      <c r="L57" t="n">
+        <v>21.73751135331517</v>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>鹽水空白</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>鹽水養樂多</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
